--- a/3DLv3/Plan/嘘情報× スケジュール.xlsx
+++ b/3DLv3/Plan/嘘情報× スケジュール.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{6E415CE7-6A31-4F55-A4DB-89EEDF18F9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03C53FC1-B014-4659-A031-D4AFA0B93ACA}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{6E415CE7-6A31-4F55-A4DB-89EEDF18F9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{329E661C-2CC6-4A20-A47E-7F4F479CE68E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2717,6 +2717,9 @@
     <xf numFmtId="0" fontId="2" fillId="24" borderId="9" xfId="34" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -2725,9 +2728,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6834,10 +6834,10 @@
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="126" t="s">
+      <c r="B2" s="123" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="126"/>
+      <c r="C2" s="123"/>
       <c r="I2" s="29" t="s">
         <v>20</v>
       </c>
@@ -6869,164 +6869,164 @@
       <c r="E4" s="3">
         <v>1</v>
       </c>
-      <c r="I4" s="123">
+      <c r="I4" s="124">
         <f>I5</f>
         <v>46314</v>
       </c>
-      <c r="J4" s="124"/>
-      <c r="K4" s="124"/>
-      <c r="L4" s="124"/>
-      <c r="M4" s="124"/>
-      <c r="N4" s="124"/>
-      <c r="O4" s="125"/>
-      <c r="P4" s="123">
+      <c r="J4" s="125"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="125"/>
+      <c r="M4" s="125"/>
+      <c r="N4" s="125"/>
+      <c r="O4" s="126"/>
+      <c r="P4" s="124">
         <f>P5</f>
         <v>46321</v>
       </c>
-      <c r="Q4" s="124"/>
-      <c r="R4" s="124"/>
-      <c r="S4" s="124"/>
-      <c r="T4" s="124"/>
-      <c r="U4" s="124"/>
-      <c r="V4" s="125"/>
-      <c r="W4" s="123">
+      <c r="Q4" s="125"/>
+      <c r="R4" s="125"/>
+      <c r="S4" s="125"/>
+      <c r="T4" s="125"/>
+      <c r="U4" s="125"/>
+      <c r="V4" s="126"/>
+      <c r="W4" s="124">
         <f>W5</f>
         <v>46328</v>
       </c>
-      <c r="X4" s="124"/>
-      <c r="Y4" s="124"/>
-      <c r="Z4" s="124"/>
-      <c r="AA4" s="124"/>
-      <c r="AB4" s="124"/>
-      <c r="AC4" s="125"/>
-      <c r="AD4" s="123">
+      <c r="X4" s="125"/>
+      <c r="Y4" s="125"/>
+      <c r="Z4" s="125"/>
+      <c r="AA4" s="125"/>
+      <c r="AB4" s="125"/>
+      <c r="AC4" s="126"/>
+      <c r="AD4" s="124">
         <f>AD5</f>
         <v>46335</v>
       </c>
-      <c r="AE4" s="124"/>
-      <c r="AF4" s="124"/>
-      <c r="AG4" s="124"/>
-      <c r="AH4" s="124"/>
-      <c r="AI4" s="124"/>
-      <c r="AJ4" s="125"/>
-      <c r="AK4" s="123">
+      <c r="AE4" s="125"/>
+      <c r="AF4" s="125"/>
+      <c r="AG4" s="125"/>
+      <c r="AH4" s="125"/>
+      <c r="AI4" s="125"/>
+      <c r="AJ4" s="126"/>
+      <c r="AK4" s="124">
         <f>AK5</f>
         <v>46342</v>
       </c>
-      <c r="AL4" s="124"/>
-      <c r="AM4" s="124"/>
-      <c r="AN4" s="124"/>
-      <c r="AO4" s="124"/>
-      <c r="AP4" s="124"/>
-      <c r="AQ4" s="125"/>
-      <c r="AR4" s="123">
+      <c r="AL4" s="125"/>
+      <c r="AM4" s="125"/>
+      <c r="AN4" s="125"/>
+      <c r="AO4" s="125"/>
+      <c r="AP4" s="125"/>
+      <c r="AQ4" s="126"/>
+      <c r="AR4" s="124">
         <f>AR5</f>
         <v>46349</v>
       </c>
-      <c r="AS4" s="124"/>
-      <c r="AT4" s="124"/>
-      <c r="AU4" s="124"/>
-      <c r="AV4" s="124"/>
-      <c r="AW4" s="124"/>
-      <c r="AX4" s="125"/>
-      <c r="AY4" s="123">
+      <c r="AS4" s="125"/>
+      <c r="AT4" s="125"/>
+      <c r="AU4" s="125"/>
+      <c r="AV4" s="125"/>
+      <c r="AW4" s="125"/>
+      <c r="AX4" s="126"/>
+      <c r="AY4" s="124">
         <f>AY5</f>
         <v>46356</v>
       </c>
-      <c r="AZ4" s="124"/>
-      <c r="BA4" s="124"/>
-      <c r="BB4" s="124"/>
-      <c r="BC4" s="124"/>
-      <c r="BD4" s="124"/>
-      <c r="BE4" s="125"/>
-      <c r="BF4" s="123">
+      <c r="AZ4" s="125"/>
+      <c r="BA4" s="125"/>
+      <c r="BB4" s="125"/>
+      <c r="BC4" s="125"/>
+      <c r="BD4" s="125"/>
+      <c r="BE4" s="126"/>
+      <c r="BF4" s="124">
         <f>BF5</f>
         <v>46363</v>
       </c>
-      <c r="BG4" s="124"/>
-      <c r="BH4" s="124"/>
-      <c r="BI4" s="124"/>
-      <c r="BJ4" s="124"/>
-      <c r="BK4" s="124"/>
-      <c r="BL4" s="125"/>
-      <c r="BM4" s="123">
+      <c r="BG4" s="125"/>
+      <c r="BH4" s="125"/>
+      <c r="BI4" s="125"/>
+      <c r="BJ4" s="125"/>
+      <c r="BK4" s="125"/>
+      <c r="BL4" s="126"/>
+      <c r="BM4" s="124">
         <f>BM5</f>
         <v>46370</v>
       </c>
-      <c r="BN4" s="124"/>
-      <c r="BO4" s="124"/>
-      <c r="BP4" s="124"/>
-      <c r="BQ4" s="124"/>
-      <c r="BR4" s="124"/>
-      <c r="BS4" s="125"/>
-      <c r="BT4" s="123">
+      <c r="BN4" s="125"/>
+      <c r="BO4" s="125"/>
+      <c r="BP4" s="125"/>
+      <c r="BQ4" s="125"/>
+      <c r="BR4" s="125"/>
+      <c r="BS4" s="126"/>
+      <c r="BT4" s="124">
         <f>BT5</f>
         <v>46377</v>
       </c>
-      <c r="BU4" s="124"/>
-      <c r="BV4" s="124"/>
-      <c r="BW4" s="124"/>
-      <c r="BX4" s="124"/>
-      <c r="BY4" s="124"/>
-      <c r="BZ4" s="125"/>
-      <c r="CA4" s="123">
+      <c r="BU4" s="125"/>
+      <c r="BV4" s="125"/>
+      <c r="BW4" s="125"/>
+      <c r="BX4" s="125"/>
+      <c r="BY4" s="125"/>
+      <c r="BZ4" s="126"/>
+      <c r="CA4" s="124">
         <f>CA5</f>
         <v>46384</v>
       </c>
-      <c r="CB4" s="124"/>
-      <c r="CC4" s="124"/>
-      <c r="CD4" s="124"/>
-      <c r="CE4" s="124"/>
-      <c r="CF4" s="124"/>
-      <c r="CG4" s="125"/>
-      <c r="CH4" s="123">
+      <c r="CB4" s="125"/>
+      <c r="CC4" s="125"/>
+      <c r="CD4" s="125"/>
+      <c r="CE4" s="125"/>
+      <c r="CF4" s="125"/>
+      <c r="CG4" s="126"/>
+      <c r="CH4" s="124">
         <f>CH5</f>
         <v>46391</v>
       </c>
-      <c r="CI4" s="124"/>
-      <c r="CJ4" s="124"/>
-      <c r="CK4" s="124"/>
-      <c r="CL4" s="124"/>
-      <c r="CM4" s="124"/>
-      <c r="CN4" s="125"/>
-      <c r="CO4" s="123">
+      <c r="CI4" s="125"/>
+      <c r="CJ4" s="125"/>
+      <c r="CK4" s="125"/>
+      <c r="CL4" s="125"/>
+      <c r="CM4" s="125"/>
+      <c r="CN4" s="126"/>
+      <c r="CO4" s="124">
         <f>CO5</f>
         <v>46398</v>
       </c>
-      <c r="CP4" s="124"/>
-      <c r="CQ4" s="124"/>
-      <c r="CR4" s="124"/>
-      <c r="CS4" s="124"/>
-      <c r="CT4" s="124"/>
-      <c r="CU4" s="125"/>
-      <c r="CV4" s="123">
+      <c r="CP4" s="125"/>
+      <c r="CQ4" s="125"/>
+      <c r="CR4" s="125"/>
+      <c r="CS4" s="125"/>
+      <c r="CT4" s="125"/>
+      <c r="CU4" s="126"/>
+      <c r="CV4" s="124">
         <f>CV5</f>
         <v>46405</v>
       </c>
-      <c r="CW4" s="124"/>
-      <c r="CX4" s="124"/>
-      <c r="CY4" s="124"/>
-      <c r="CZ4" s="124"/>
-      <c r="DA4" s="124"/>
-      <c r="DB4" s="125"/>
-      <c r="DC4" s="123">
+      <c r="CW4" s="125"/>
+      <c r="CX4" s="125"/>
+      <c r="CY4" s="125"/>
+      <c r="CZ4" s="125"/>
+      <c r="DA4" s="125"/>
+      <c r="DB4" s="126"/>
+      <c r="DC4" s="124">
         <f>DC5</f>
         <v>46412</v>
       </c>
-      <c r="DD4" s="124"/>
-      <c r="DE4" s="124"/>
-      <c r="DF4" s="124"/>
-      <c r="DG4" s="124"/>
-      <c r="DH4" s="124"/>
-      <c r="DI4" s="125"/>
-      <c r="DJ4" s="123">
+      <c r="DD4" s="125"/>
+      <c r="DE4" s="125"/>
+      <c r="DF4" s="125"/>
+      <c r="DG4" s="125"/>
+      <c r="DH4" s="125"/>
+      <c r="DI4" s="126"/>
+      <c r="DJ4" s="124">
         <f>DJ5</f>
         <v>46419</v>
       </c>
-      <c r="DK4" s="124"/>
-      <c r="DL4" s="124"/>
-      <c r="DM4" s="124"/>
-      <c r="DN4" s="124"/>
+      <c r="DK4" s="125"/>
+      <c r="DL4" s="125"/>
+      <c r="DM4" s="125"/>
+      <c r="DN4" s="125"/>
     </row>
     <row r="5" spans="1:118" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -9275,8 +9275,8 @@
       <c r="C17" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="39">
-        <v>0</v>
+      <c r="D17" s="36">
+        <v>1</v>
       </c>
       <c r="E17" s="63">
         <f>F15+1</f>
@@ -9410,8 +9410,8 @@
       <c r="C18" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="39">
-        <v>0</v>
+      <c r="D18" s="36">
+        <v>1</v>
       </c>
       <c r="E18" s="63">
         <f>F17</f>
@@ -9545,8 +9545,8 @@
       <c r="C19" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="39">
-        <v>0</v>
+      <c r="D19" s="36">
+        <v>1</v>
       </c>
       <c r="E19" s="63">
         <f>F18</f>
@@ -9680,8 +9680,8 @@
       <c r="C20" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="39">
-        <v>0</v>
+      <c r="D20" s="36">
+        <v>1</v>
       </c>
       <c r="E20" s="63">
         <f>F19+1</f>
@@ -9815,8 +9815,8 @@
       <c r="C21" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="39">
-        <v>0</v>
+      <c r="D21" s="36">
+        <v>1</v>
       </c>
       <c r="E21" s="63">
         <f>F20</f>
@@ -9950,8 +9950,8 @@
       <c r="C22" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="39">
-        <v>0</v>
+      <c r="D22" s="36">
+        <v>1</v>
       </c>
       <c r="E22" s="63">
         <f>F21</f>
@@ -10085,8 +10085,8 @@
       <c r="C23" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="39">
-        <v>0</v>
+      <c r="D23" s="36">
+        <v>1</v>
       </c>
       <c r="E23" s="63">
         <f>F22+3</f>
@@ -10220,8 +10220,8 @@
       <c r="C24" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="39">
-        <v>0</v>
+      <c r="D24" s="36">
+        <v>1</v>
       </c>
       <c r="E24" s="63">
         <f>F23</f>
@@ -24730,6 +24730,10 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="CV4:DB4"/>
+    <mergeCell ref="DC4:DI4"/>
+    <mergeCell ref="DJ4:DN4"/>
+    <mergeCell ref="CO4:CU4"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="BM4:BS4"/>
     <mergeCell ref="BT4:BZ4"/>
@@ -24746,13 +24750,9 @@
     <mergeCell ref="AK4:AQ4"/>
     <mergeCell ref="AR4:AX4"/>
     <mergeCell ref="AY4:BE4"/>
-    <mergeCell ref="CV4:DB4"/>
-    <mergeCell ref="DC4:DI4"/>
-    <mergeCell ref="DJ4:DN4"/>
-    <mergeCell ref="CO4:CU4"/>
   </mergeCells>
   <phoneticPr fontId="26"/>
-  <conditionalFormatting sqref="D7:D28 D30:D35 D43:D48">
+  <conditionalFormatting sqref="D30:D35 D43:D48 D7:D28">
     <cfRule type="dataBar" priority="355">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -26575,7 +26575,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D7:D28 D30:D35 D43:D48</xm:sqref>
+          <xm:sqref>D30:D35 D43:D48 D7:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{97D24A29-56E5-4171-8BD7-EBEA659962A8}">
@@ -27123,35 +27123,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -27439,27 +27410,36 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5144944C-1F1D-4162-962A-96F3FC8455D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{708DBB9E-6D89-4A94-9DC5-964B7833E11C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27478,4 +27458,24 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5144944C-1F1D-4162-962A-96F3FC8455D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>